--- a/data/statcan_windsor_area_monthly.xlsx
+++ b/data/statcan_windsor_area_monthly.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Windsor-area combined" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GHIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMB+DWT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BWB (Sarnia)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="All Windsor-area combined" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GHIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AMB+DWT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BWB (Sarnia)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3551,7 +3551,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:48 UTC</t>
+          <t>Rebuilt: 2026-09-11 19:51 UTC</t>
         </is>
       </c>
     </row>

--- a/data/statcan_windsor_area_monthly.xlsx
+++ b/data/statcan_windsor_area_monthly.xlsx
@@ -3551,7 +3551,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:51 UTC</t>
+          <t>Rebuilt: 2026-09-11 19:59 UTC</t>
         </is>
       </c>
     </row>

--- a/data/statcan_windsor_area_monthly.xlsx
+++ b/data/statcan_windsor_area_monthly.xlsx
@@ -3551,7 +3551,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:59 UTC</t>
+          <t>Rebuilt: 2026-09-11 20:09 UTC</t>
         </is>
       </c>
     </row>

--- a/data/statcan_windsor_area_monthly.xlsx
+++ b/data/statcan_windsor_area_monthly.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1387,6 +1387,36 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>598168</v>
+      </c>
+      <c r="C34" t="n">
+        <v>346740</v>
+      </c>
+      <c r="D34" t="n">
+        <v>244749</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.1155084861132091</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.03373948715502514</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.258479020979021</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1398,7 +1428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1509,6 +1539,29 @@
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>175148</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100168</v>
+      </c>
+      <c r="D4" t="n">
+        <v>72503</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1520,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1688,15 +1741,9 @@
       <c r="D6" t="n">
         <v>155692</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1.532513977995929</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1.617536693107871</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.374910383330537</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" t="n">
         <v>31</v>
       </c>
@@ -1718,13 +1765,13 @@
         <v>191395</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1018439657856659</v>
+        <v>1.67281471978318</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.08660521791076783</v>
+        <v>1.785407177634679</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1250124906687357</v>
+        <v>1.528168548972987</v>
       </c>
       <c r="H7" t="n">
         <v>30</v>
@@ -2484,6 +2531,35 @@
         <v>31</v>
       </c>
       <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>286401</v>
+      </c>
+      <c r="C34" t="n">
+        <v>186599</v>
+      </c>
+      <c r="D34" t="n">
+        <v>97472</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>-0.3200904960188399</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-0.3374156230137453</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>-0.2790319240214207</v>
+      </c>
+      <c r="H34" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2496,7 +2572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2664,15 +2740,9 @@
       <c r="D6" t="n">
         <v>72108</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>1.354302299263756</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1.54707055597108</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.12984404536862</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" t="n">
         <v>31</v>
       </c>
@@ -2694,13 +2764,13 @@
         <v>102454</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01982655809008834</v>
+        <v>1.446324319426286</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.02483778778103497</v>
+        <v>1.774497758592064</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.0158745897494373</v>
+        <v>1.228859834228903</v>
       </c>
       <c r="H7" t="n">
         <v>30</v>
@@ -3460,6 +3530,35 @@
         <v>31</v>
       </c>
       <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>136619</v>
+      </c>
+      <c r="C34" t="n">
+        <v>59973</v>
+      </c>
+      <c r="D34" t="n">
+        <v>74774</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.1880429583894952</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0.1147397769516729</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0.2612846636529249</v>
+      </c>
+      <c r="H34" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3551,7 +3650,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 20:09 UTC</t>
+          <t>Rebuilt: 2026-10-13 19:51 UTC</t>
         </is>
       </c>
     </row>
